--- a/docs/sdlc/10_requirements/WS2D-RD-001_要件一覧.xlsx
+++ b/docs/sdlc/10_requirements/WS2D-RD-001_要件一覧.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. ステークホルダーと役割'!$A$1:$F$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6.2 ユースケース一覧表'!$A$1:$E$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'7. 業務フロー'!$A$1:$C$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'9. 機能要件一覧（51件）'!$A$1:$G$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'9. 機能要件一覧（51件）'!$A$1:$G$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'9.1 機能要件のグルーピング（参考）'!$A$1:$C$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'11. 非機能要件の概要'!$A$1:$B$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'14. 要件に関わるリスクと対応方針'!$A$1:$E$20</definedName>
@@ -2764,14 +2764,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>auth/login.html, setup.html, account.html, signup.html</t>
+          <t>auth/login.html, setup.html, signup.html, partials/view-account.html</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>利用者とワークスペースの所属・ロール（owner/admin/member）を管理する</t>
+          <t>利用者とワークスペースの所属・ロール（一般/管理者）を管理する</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>auth/user.html, auth/tenant.html, admin/console.html</t>
+          <t>auth/tenant.html, admin/console.html</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>auth/account.html</t>
+          <t>partials/view-account.html</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -3038,17 +3038,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>`autorun`</t>
+          <t>`user_menu_feedback`</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>AutoRun</t>
+          <t>ユーザーメニューと利用者フィードバック送信</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>解析→クロール→QA生成→テスト実行を一つのフローで行う</t>
+          <t>トップバーから個人設定・ガイド・フィードバック・ログアウトへ移動し、不具合や要望を送る</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -3058,145 +3058,145 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>view-auto-run.html</t>
+          <t>partials/topbar.html, partials/view-account.html, partials/view-feedback.html</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/auto_run.py`</t>
+          <t>`web/routes/feedback.py`</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>`web/services/spec_ts_generator.py`, `web/services/playwright_executor.py`</t>
+          <t>`web/services/feedback_store.py`</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>`diff_history`</t>
+          <t>`autorun`</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>差分 / 履歴 / 再クロール</t>
+          <t>AutoRun</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>再クロールし前回スナップショットとの仕様ドリフトを検出する</t>
+          <t>解析→クロール→QA生成→テスト実行を一つのフローで行う</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>history.js, recrawl.js, results.js</t>
+          <t>view-auto-run.html</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/history.py`, `site.py`, `runs.py`</t>
+          <t>`web/routes/auto_run.py`</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>`src/diff/snapshot.py`, `src/diff/differ.py`</t>
+          <t>`web/services/spec_ts_generator.py`, `web/services/playwright_executor.py`</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>`settings`</t>
+          <t>`diff_history`</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>設定</t>
+          <t>差分 / 履歴 / 再クロール</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>LLMキー等の環境設定を管理する</t>
+          <t>再クロールし前回スナップショットとの仕様ドリフトを検出する</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>view-settings.html</t>
+          <t>history.js, recrawl.js, results.js</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/settings.py`, `pages.py`</t>
+          <t>`web/routes/history.py`, `site.py`, `runs.py`</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>`web/env_store.py`</t>
+          <t>`src/diff/snapshot.py`, `src/diff/differ.py`</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>`usage_roi`</t>
+          <t>`settings`</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ROIダッシュボード / 利用実績</t>
+          <t>設定</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>利用実績から削減工数（時間・円）を推定表示する</t>
+          <t>LLMキー等の環境設定を管理する</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>view-usage.html</t>
+          <t>view-settings.html</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/usage.py`</t>
+          <t>`web/routes/settings.py`, `pages.py`</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>`web/services/usage_tracker.py`</t>
+          <t>`web/env_store.py`</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>`coverage_gap_report`</t>
+          <t>`usage_roi`</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>カバレッジと未確認領域</t>
+          <t>ROIダッシュボード / 利用実績</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>網羅性証明として未確認領域を可視化する</t>
+          <t>利用実績から削減工数（時間・円）を推定表示する</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3206,71 +3206,71 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>report.html内セクション</t>
+          <t>view-usage.html</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>（レポート生成に統合、専用APIなし）</t>
+          <t>`web/routes/usage.py`</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>`src/generator/coverage_gap.py`</t>
+          <t>`web/services/usage_tracker.py`</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>`doc_fusion`</t>
+          <t>`coverage_gap_report`</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>文書×実測突合（Doc Fusion）</t>
+          <t>カバレッジと未確認領域</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>既存仕様書等の参考文書と実測結果を突合しギャップを検出する</t>
+          <t>網羅性証明として未確認領域を可視化する</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>view-generate.html（doc-fusion.js）</t>
+          <t>report.html内セクション</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/crawl.py`, `traceability.py`</t>
+          <t>（レポート生成に統合、専用APIなし）</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>`src/ingest/loader.py`, `src/ingest/matcher.py`</t>
+          <t>`src/generator/coverage_gap.py`</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>`exploration_capture`</t>
+          <t>`doc_fusion`</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>探索セッション記録 / カバレッジヒートマップ</t>
+          <t>文書×実測突合（Doc Fusion）</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>手動探索操作を記録しカバレッジをヒートマップ化する</t>
+          <t>既存仕様書等の参考文書と実測結果を突合しギャップを検出する</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3280,71 +3280,71 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>（report経由、専用画面なし）</t>
+          <t>view-generate.html（doc-fusion.js）</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/report.py`</t>
+          <t>`web/routes/crawl.py`, `traceability.py`</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>`src/capture/session_recorder.py`, `src/capture/coverage.py`</t>
+          <t>`src/ingest/loader.py`, `src/ingest/matcher.py`</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>`reverse_assets`</t>
+          <t>`exploration_capture`</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>リバース（記録セッション→テスト資産逆生成）</t>
+          <t>探索セッション記録 / カバレッジヒートマップ</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>記録済み探索セッションからテスト資産を逆生成する</t>
+          <t>手動探索操作を記録しカバレッジをヒートマップ化する</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>（report経由、専用画面なし）</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>なし（内部生成）</t>
+          <t>`web/routes/report.py`</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>`src/capture/reverse_generator.py`</t>
+          <t>`src/capture/session_recorder.py`, `src/capture/coverage.py`</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>`field_definition_bva`</t>
+          <t>`reverse_assets`</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>項目定義書＋境界値分析（BVA）</t>
+          <t>リバース（記録セッション→テスト資産逆生成）</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>入力項目の境界値テストデータを自動生成する</t>
+          <t>記録済み探索セッションからテスト資産を逆生成する</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>なし（spec.xlsxへ出力）</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3364,24 +3364,24 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>`src/analyzer/bva.py`</t>
+          <t>`src/capture/reverse_generator.py`</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>`finding_ticket`</t>
+          <t>`field_definition_bva`</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>気づきマーク→再現手順付きバグ票</t>
+          <t>項目定義書＋境界値分析（BVA）</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>探索中の気づきを再現手順付きバグ票として出力する</t>
+          <t>入力項目の境界値テストデータを自動生成する</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>なし（spec.xlsxへ出力）</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>`src/capture/finding_reporter.py`</t>
+          <t>`src/analyzer/bva.py`</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>`test_plan`</t>
+          <t>`finding_ticket`</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>テスト計画ドラフト生成</t>
+          <t>気づきマーク→再現手順付きバグ票</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>インベントリ×ROI係数から工数見積・スコープ表を生成する</t>
+          <t>探索中の気づきを再現手順付きバグ票として出力する</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3433,34 +3433,34 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/qa_process.py`</t>
+          <t>なし（内部生成）</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>`src/generator/test_plan_generator.py`</t>
+          <t>`src/capture/finding_reporter.py`</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>`ci_warnings_cleanup`</t>
+          <t>`test_plan`</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CI警告一掃</t>
+          <t>テスト計画ドラフト生成</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>pytest収集警告・Pillow非推奨警告を解消し再発を防止する</t>
+          <t>インベントリ×ROI係数から工数見積・スコープ表を生成する</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -3470,140 +3470,140 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>なし（内部品質）</t>
+          <t>`web/routes/qa_process.py`</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>`src/diff/screenshot_diff.py`, `src/llm/viewpoint_generator.py`</t>
+          <t>`src/generator/test_plan_generator.py`</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>`old_new_comparison`</t>
+          <t>`ci_warnings_cleanup`</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>現新比較モード</t>
+          <t>CI警告一掃</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>移行前後のサイトを比較し差分を検証する</t>
+          <t>pytest収集警告・Pillow非推奨警告を解消し再発を防止する</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>view-compare.js</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/history.py`</t>
+          <t>なし（内部品質）</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>`src/diff/pair_matcher.py`, `src/diff/comparison.py`</t>
+          <t>`src/diff/screenshot_diff.py`, `src/llm/viewpoint_generator.py`</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>`ux_review`</t>
+          <t>`old_new_comparison`</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>UX自動エキスパートレビュー</t>
+          <t>現新比較モード</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>axe-core＋ニールセン10原則によるUX所見を生成する</t>
+          <t>移行前後のサイトを比較し差分を検証する</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>report.html「UX所見」タブ</t>
+          <t>view-compare.js</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>なし（内部生成）</t>
+          <t>`web/routes/history.py`</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>`src/ux/axe_runner.py`, `src/ux/heuristics.py`</t>
+          <t>`src/diff/pair_matcher.py`, `src/diff/comparison.py`</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>`snapshot_retention`</t>
+          <t>`ux_review`</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>スナップショット保持・容量・バックアップ運用</t>
+          <t>UX自動エキスパートレビュー</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>保持ポリシーに基づきスナップショットを自動整理する</t>
+          <t>axe-core＋ニールセン10原則によるUX所見を生成する</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>view-settings.html</t>
+          <t>report.html「UX所見」タブ</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/admin.py`</t>
+          <t>なし（内部生成）</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>`web/services/retention.py`</t>
+          <t>`src/ux/axe_runner.py`, `src/ux/heuristics.py`</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>`admin_audit`</t>
+          <t>`snapshot_retention`</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>管理操作のテナント監査ログ</t>
+          <t>スナップショット保持・容量・バックアップ運用</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>管理操作を監査ログに記録する</t>
+          <t>保持ポリシーに基づきスナップショットを自動整理する</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3618,29 +3618,29 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/admin.py` 他複数</t>
+          <t>`web/routes/admin.py`</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>`web/services/admin_audit.py`</t>
+          <t>`web/services/retention.py`</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>`ci_drift_monitor`</t>
+          <t>`admin_audit`</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Drift Check as Code</t>
+          <t>管理操作のテナント監査ログ</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CI組み込みのドリフト監視とSlack通知を行う</t>
+          <t>管理操作を監査ログに記録する</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3655,76 +3655,76 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>CIワークフロー経由（専用routeなし）</t>
+          <t>`web/routes/admin.py` 他複数</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>`src/ci_drift.py`, `web/services/drift_summary.py`</t>
+          <t>`web/services/admin_audit.py`</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>`document_mbt`</t>
+          <t>`ci_drift_monitor`</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>文書駆動MBT</t>
+          <t>Drift Check as Code</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>参考文書の要件と実測を突合しMBTモデルからテスト設計する</t>
+          <t>CI組み込みのドリフト監視とSlack通知を行う</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>view-auto-run.html（autorun-document.js）</t>
+          <t>view-settings.html</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/auto_run.py`</t>
+          <t>CIワークフロー経由（専用routeなし）</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>`src/mbt/document_model.py`, `src/mbt/manual_procedures.py`</t>
+          <t>`src/ci_drift.py`, `web/services/drift_summary.py`</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>`evidence_pack`</t>
+          <t>`document_mbt`</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>検収・監査向けテスト実施証跡パック</t>
+          <t>文書駆動MBT</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>テスト実施の証跡をパック化して出力する</t>
+          <t>参考文書の要件と実測を突合しMBTモデルからテスト設計する</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>（autorun.js経由）</t>
+          <t>view-auto-run.html（autorun-document.js）</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3734,24 +3734,24 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>`src/evidence/pack_model.py`</t>
+          <t>`src/mbt/document_model.py`, `src/mbt/manual_procedures.py`</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>`diff_severity`</t>
+          <t>`evidence_pack`</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>差分の重要度判定と誤検知フィルタ</t>
+          <t>検収・監査向けテスト実施証跡パック</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>差分に重要度を付与し除外ルールで誤検知を抑制する</t>
+          <t>テスト実施の証跡をパック化して出力する</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3761,34 +3761,34 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>なし（diff_report.htmlへ出力）</t>
+          <t>（autorun.js経由）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>なし（内部生成）</t>
+          <t>`web/routes/auto_run.py`</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>`src/diff/severity.py`, `src/diff/ignore_rules.py`</t>
+          <t>`src/evidence/pack_model.py`</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>`api_v1_openapi`</t>
+          <t>`diff_severity`</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>REST API拡充とOpenAPI公開</t>
+          <t>差分の重要度判定と誤検知フィルタ</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>`/api/v1` 系REST APIとOpenAPI仕様を公開する</t>
+          <t>差分に重要度を付与し除外ルールで誤検知を抑制する</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3798,39 +3798,39 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>なし（diff_report.htmlへ出力）</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/api_v1.py`, `api_v1_schedule.py`</t>
+          <t>なし（内部生成）</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>`web/services/openapi_spec.py`</t>
+          <t>`src/diff/severity.py`, `src/diff/ignore_rules.py`</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>`multi_viewport`</t>
+          <t>`api_v1_openapi`</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>マルチビューポート仕様書</t>
+          <t>REST API拡充とOpenAPI公開</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>複数画面幅でのレイアウト差分を検証する</t>
+          <t>`/api/v1` 系REST APIとOpenAPI仕様を公開する</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3840,34 +3840,34 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>なし（内部生成）</t>
+          <t>`web/routes/api_v1.py`, `api_v1_schedule.py`</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>`src/viewport/profiles.py`, `src/viewport/comparison.py`</t>
+          <t>`web/services/openapi_spec.py`</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>`sso_oidc`</t>
+          <t>`multi_viewport`</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SSO（OIDC）</t>
+          <t>マルチビューポート仕様書</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>OIDCによるシングルサインオンとAPIトークンスコープを提供する</t>
+          <t>複数画面幅でのレイアウト差分を検証する</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3877,34 +3877,34 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/oidc.py`</t>
+          <t>なし（内部生成）</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>`web/services/oidc.py`</t>
+          <t>`src/viewport/profiles.py`, `src/viewport/comparison.py`</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>`observability`</t>
+          <t>`sso_oidc`</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>可観測性</t>
+          <t>SSO（OIDC）</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Prometheusメトリクス・構造化ログを提供する</t>
+          <t>OIDCによるシングルサインオンとAPIトークンスコープを提供する</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3914,29 +3914,29 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/metrics.py`</t>
+          <t>`web/routes/oidc.py`</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>`web/services/metrics.py`</t>
+          <t>`web/services/oidc.py`</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>`api_spec_recovery`</t>
+          <t>`observability`</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>API仕様の逆生成</t>
+          <t>可観測性</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>実測から画面↔API対応表・OpenAPI雛形を逆生成する</t>
+          <t>Prometheusメトリクス・構造化ログを提供する</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3951,29 +3951,29 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>なし（内部生成）</t>
+          <t>`web/routes/metrics.py`</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>`src/apispec/recovery.py`</t>
+          <t>`web/services/metrics.py`</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>`screen_coverage_map`</t>
+          <t>`api_spec_recovery`</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>画面カバレッジマップ</t>
+          <t>API仕様の逆生成</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>画面のテスト実行網羅状況をマップ化する</t>
+          <t>実測から画面↔API対応表・OpenAPI雛形を逆生成する</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3993,29 +3993,29 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>`src/apispec/coverage_map.py`</t>
+          <t>`src/apispec/recovery.py`</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>`wording_consistency`</t>
+          <t>`screen_coverage_map`</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>文言一貫性・表記ゆれチェック</t>
+          <t>画面カバレッジマップ</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>サイト内文言の表記ゆれを検出する</t>
+          <t>画面のテスト実行網羅状況をマップ化する</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4030,29 +4030,29 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>`src/wording/consistency.py`</t>
+          <t>`src/apispec/coverage_map.py`</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>`full_archive`</t>
+          <t>`wording_consistency`</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>完全アーカイブと外形監視</t>
+          <t>文言一貫性・表記ゆれチェック</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>sitemap/PDF等を含む完全アーカイブと外形監視を行う</t>
+          <t>サイト内文言の表記ゆれを検出する</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4067,24 +4067,24 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>`src/archive/full_archive.py`, `src/archive/external_monitor.py`</t>
+          <t>`src/wording/consistency.py`</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>`qa_assistant_chat`</t>
+          <t>`full_archive`</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>QAアシスタント（LLMチャット）</t>
+          <t>完全アーカイブと外形監視</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>LLMへのQA相談チャットを提供する</t>
+          <t>sitemap/PDF等を含む完全アーカイブと外形監視を行う</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4094,182 +4094,182 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>view-auto-run.html（autorun-chat.js）</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/llm_chat.py`</t>
+          <t>なし（内部生成）</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>`src/llm/openai_client.py`</t>
+          <t>`src/archive/full_archive.py`, `src/archive/external_monitor.py`</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>`autorun_stage_approval`</t>
+          <t>`qa_assistant_chat`</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>AutoRun 段階承認パイプライン</t>
+          <t>QAアシスタント（LLMチャット）</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>テスト目的〜テストケースまでを段階的に人間承認する</t>
+          <t>LLMへのQA相談チャットを提供する</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>view-auto-run.html（autorun-stages.js）</t>
+          <t>view-auto-run.html（autorun-chat.js）</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/autorun_stages.py`</t>
+          <t>`web/routes/llm_chat.py`</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>`src/autorun/automation_plan.py`, `src/autorun/stages.py`</t>
+          <t>`src/llm/openai_client.py`</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>`autorun_result_report`</t>
+          <t>`autorun_stage_approval`</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>AutoRun 実行結果レポート専用ページ</t>
+          <t>AutoRun 段階承認パイプライン</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>実行結果を専用ページでダッシュボード表示する</t>
+          <t>テスト目的〜テストケースまでを段階的に人間承認する</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>autorun-report.html</t>
+          <t>view-auto-run.html（autorun-stages.js）</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/autorun_report.py`</t>
+          <t>`web/routes/autorun_stages.py`</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>`src/autorun/qf_schema.py`</t>
+          <t>`src/autorun/automation_plan.py`, `src/autorun/stages.py`</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>`autorun_security_kernel`</t>
+          <t>`autorun_result_report`</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>AutoRun セキュリティカーネル</t>
+          <t>AutoRun 実行結果レポート専用ページ</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>送信ゲートウェイと非信頼コンテンツ境界を提供する</t>
+          <t>実行結果を専用ページでダッシュボード表示する</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>autorun-report.html</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>なし（内部機構）</t>
+          <t>`web/routes/autorun_report.py`</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>`web/services/egress_gateway.py`, `web/services/untrusted_content.py`</t>
+          <t>`src/autorun/qf_schema.py`</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>`autorun_self_check`</t>
+          <t>`autorun_security_kernel`</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>AutoRun 自己検証（ミューテーションテスト）</t>
+          <t>AutoRun セキュリティカーネル</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>生成テストの検出力をミューテーションテストで自己検証する</t>
+          <t>送信ゲートウェイと非信頼コンテンツ境界を提供する</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>autorun-report.js</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/auto_run.py`</t>
+          <t>なし（内部機構）</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>`web/services/mutation_verifier.py`</t>
+          <t>`web/services/egress_gateway.py`, `web/services/untrusted_content.py`</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>`autorun_nonfunctional_judge`</t>
+          <t>`autorun_self_check`</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>AutoRun 非機能判定・観測完全性</t>
+          <t>AutoRun 自己検証（ミューテーションテスト）</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>非機能の基準線との合否判定と未観測領域を明示する</t>
+          <t>生成テストの検出力をミューテーションテストで自己検証する</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4289,66 +4289,66 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>`web/services/nonfunctional_judge.py`, `web/services/observation_coverage.py`</t>
+          <t>`web/services/mutation_verifier.py`</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>`ui_visual_complexity`</t>
+          <t>`autorun_nonfunctional_judge`</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>UI 視覚的複雑性の実測・回帰検知</t>
+          <t>AutoRun 非機能判定・観測完全性</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>画面の視覚的複雑性を実測し回帰を検知する</t>
+          <t>非機能の基準線との合否判定と未観測領域を明示する</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>autorun-report.js</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>なし（内部生成）</t>
+          <t>`web/routes/auto_run.py`</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>`web/services/visual_complexity.py`</t>
+          <t>`web/services/nonfunctional_judge.py`, `web/services/observation_coverage.py`</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>`autorun_failure_triage`</t>
+          <t>`ui_visual_complexity`</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>AutoRun 失敗の原因特定</t>
+          <t>UI 視覚的複雑性の実測・回帰検知</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>失敗の原因候補を特定し技法適用結果を提示する</t>
+          <t>画面の視覚的複雑性を実測し回帰を検知する</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -4358,29 +4358,29 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/auto_run.py`</t>
+          <t>なし（内部生成）</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>`web/services/failure_hypothesis.py`</t>
+          <t>`web/services/visual_complexity.py`</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>`technique_engine`</t>
+          <t>`autorun_failure_triage`</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>テスト技法エンジン</t>
+          <t>AutoRun 失敗の原因特定</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>t-way被覆配列の正準実装と性質検証器を提供する</t>
+          <t>失敗の原因候補を特定し技法適用結果を提示する</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>なし（内部生成）</t>
+          <t>`web/routes/auto_run.py`</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>`src/techniques/combinatorial.py`, `src/techniques/verify.py`</t>
+          <t>`web/services/failure_hypothesis.py`</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>`autorun_extended_techniques`</t>
+          <t>`technique_engine`</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>テスト技法の網羅的適用</t>
+          <t>テスト技法エンジン</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>分類ツリー法・直交表等6技法を適用する</t>
+          <t>t-way被覆配列の正準実装と性質検証器を提供する</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -4427,34 +4427,34 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>view-auto-run.html（autorun-stages.js）</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/autorun_stages.py`</t>
+          <t>なし（内部生成）</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>`src/autorun/classification_tree.py`, `src/autorun/orthogonal_array.py`</t>
+          <t>`src/techniques/combinatorial.py`, `src/techniques/verify.py`</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>`state_transition_table`</t>
+          <t>`autorun_extended_techniques`</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>状態遷移表</t>
+          <t>テスト技法の網羅的適用</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>ISTQB状態遷移テストの標準テーブルを生成する</t>
+          <t>分類ツリー法・直交表等6技法を適用する</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -4464,34 +4464,34 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>view-transition.js</t>
+          <t>view-auto-run.html（autorun-stages.js）</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/report.py`</t>
+          <t>`web/routes/autorun_stages.py`</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>`src/graph/state_table.py`</t>
+          <t>`src/autorun/classification_tree.py`, `src/autorun/orthogonal_array.py`</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>`testcase_table`</t>
+          <t>`state_transition_table`</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ローレベルテストケース表</t>
+          <t>状態遷移表</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>10列テストケース表の生成・編集・Playwright実行を行う</t>
+          <t>ISTQB状態遷移テストの標準テーブルを生成する</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -4501,145 +4501,145 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>view-testcase-grid.js</t>
+          <t>view-transition.js</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/qa_process.py`</t>
+          <t>`web/routes/report.py`</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>`src/generator/testcase_table.py`, `web/services/testcase_table_store.py`</t>
+          <t>`src/graph/state_table.py`</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>`zero_wait_sample_report`</t>
+          <t>`testcase_table`</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ゼロ待ちサンプルレポート</t>
+          <t>ローレベルテストケース表</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>同梱デモレポートを即時展開して体験可能にする</t>
+          <t>10列テストケース表の生成・編集・Playwright実行を行う</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>view-dashboard.html</t>
+          <t>view-testcase-grid.js</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/report.py`, `history.py`</t>
+          <t>`web/routes/qa_process.py`</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/report.py`, `web/config.py`</t>
+          <t>`src/generator/testcase_table.py`, `web/services/testcase_table_store.py`</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>`cli_mode`</t>
+          <t>`zero_wait_sample_report`</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CLIモード（System 03）</t>
+          <t>ゼロ待ちサンプルレポート</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>画面を使わず端末からdoc/autorun/testを実行する</t>
+          <t>同梱デモレポートを即時展開して体験可能にする</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>cli.html</t>
+          <t>view-dashboard.html</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/pages.py`（/cli）、実体は`src/cli.py`</t>
+          <t>`web/routes/report.py`, `history.py`</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>`src/cli.py`, `web/services/cli_runner.py`</t>
+          <t>`web/routes/report.py`, `web/config.py`</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>`spec_xlsx_full_export`</t>
+          <t>`cli_mode`</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>テスト仕様書一式のExcel出力（7シート）</t>
+          <t>CLIモード（System 03）</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>画面一覧〜遷移表まで7シートのExcelを一括出力する</t>
+          <t>画面を使わず端末からdoc/autorun/testを実行する</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>view-generate.html</t>
+          <t>cli.html</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/report.py`</t>
+          <t>`web/routes/pages.py`（/cli）、実体は`src/cli.py`</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>`web/services/export_xlsx.py`</t>
+          <t>`src/cli.py`, `web/services/cli_runner.py`</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>`condition_to_testcase_link`</t>
+          <t>`spec_xlsx_full_export`</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>条件⇄テストケースの接続</t>
+          <t>テスト仕様書一式のExcel出力（7シート）</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>画面別設計の条件からテストケースへ絞り込み遷移する</t>
+          <t>画面一覧〜遷移表まで7シートのExcelを一括出力する</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -4649,59 +4649,96 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>view-design.js, view-testcase-grid.js</t>
+          <t>view-generate.html</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>`web/routes/qa_process.py`</t>
+          <t>`web/routes/report.py`</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>`web/services/screen_test_design.py`</t>
+          <t>`web/services/export_xlsx.py`</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>`condition_to_testcase_link`</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>条件⇄テストケースの接続</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>画面別設計の条件からテストケースへ絞り込み遷移する</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>view-design.js, view-testcase-grid.js</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>`web/routes/qa_process.py`</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>`web/services/screen_test_design.py`</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
           <t>`condition_run_status`</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>テスト実行結果の設計への還元</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>実行結果を条件行にバッジとして反映する</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>view-design.js</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>`web/routes/qa_process.py`</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>`web/services/condition_run_status.py`</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G52"/>
+  <autoFilter ref="A1:G53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/sdlc/10_requirements/WS2D-RD-001_要件一覧.xlsx
+++ b/docs/sdlc/10_requirements/WS2D-RD-001_要件一覧.xlsx
@@ -2984,7 +2984,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>auth/tenant.html, admin/console.html</t>
+          <t>auth/tenant.html, partials/view-user-management.html</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
